--- a/Stock_Items_import.xlsx
+++ b/Stock_Items_import.xlsx
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>Hoka</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>Hoka</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>Hoka</t>
         </is>
       </c>
       <c r="C94" t="n">
